--- a/stories/arbres/ATOM-REL.PAR.001-09.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Thierry est dans le salon avec papa. Il fait rouler un train en bois. Les roues tapent le parquet. Clémentine arrive. Elle aimerait le train. Thierry peut prêter. Il dit : tu peux. C'est ton tour. Il tend le train. Clémentine pousse le wagon. Thierry attend son tour. Il s'assoit près de papa. Papa dit : on peut prêter. On peut attendre son tour. On peut proposer un autre jeu. Thierry prend des cubes. Il dit : un autre jeu, les cubes. Clémentine finit. Elle rend le train. Thierry le fait rouler. Parce qu'il a su prêter, le jeu continue. Papa tape dans ses mains.</t>
+          <t>Thierry est dans le salon avec papa. Il fait rouler un train en bois. Les roues tapent le parquet. Clémentine arrive. Elle aimerait le train. Thierry peut prêter. Tu peux. C'est ton tour. Il tend le train. Clémentine pousse le wagon. Thierry attend son tour. Il s'assoit près de papa. On peut prêter. On peut attendre son tour. On peut proposer un autre jeu. Thierry prend des cubes. Un autre jeu, les cubes. Clémentine finit. Elle rend le train. Thierry le fait rouler. Parce qu'il a su prêter, le jeu continue. Papa tape dans ses mains.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Thierry est dans le salon avec papa. Il fait rouler un train en bois. Les roues tapent le parquet. Clémentine arrive. Elle aimerait le train. Thierry peut prêter.
+narrateur|Tu peux. C'est ton tour. Il tend le train.
+narrateur|Clémentine pousse le wagon. Thierry attend son tour. Il s'assoit près de papa.
+papa|On peut prêter. On peut attendre son tour. On peut proposer un autre jeu.
+narrateur|Thierry prend des cubes.
+narrateur|Un autre jeu, les cubes.
+narrateur|Clémentine finit. Elle rend le train. Thierry le fait rouler. Parce qu'il a su prêter, le jeu continue. Papa tape dans ses mains.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Clémentine veut le train. Que peut faire Thierry ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Thierry a su prêter. Il a attendu son tour. Il a proposé un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Thierry et Clémentine rangent le train. Papa ferme la caisse.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.001-09.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Clémentine finit. Elle rend le train. Thierry le fait rouler. Parce qu'il a su prêter, le jeu continue. Papa tape dans ses mains.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Clémentine veut le train. Que peut faire Thierry ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Thierry a su prêter. Il a attendu son tour. Il a proposé un autre jeu.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Thierry et Clémentine rangent le train. Papa ferme la caisse.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.PAR.001-09.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thierry prête le train</t>
+          <t>Le train de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le parquet chante sous les roues. Raphaël pousse le train. Victorina le voudrait. Il prête, attend son tour, puis propose les cubes.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Thierry est dans le salon avec papa. Il fait rouler un train en bois. Les roues tapent le parquet. Clémentine arrive. Elle aimerait le train. Thierry peut prêter. Tu peux. C'est ton tour. Il tend le train. Clémentine pousse le wagon. Thierry attend son tour. Il s'assoit près de papa. On peut prêter. On peut attendre son tour. On peut proposer un autre jeu. Thierry prend des cubes. Un autre jeu, les cubes. Clémentine finit. Elle rend le train. Thierry le fait rouler. Parce qu'il a su prêter, le jeu continue. Papa tape dans ses mains.</t>
+          <t>Le parquet chante sous les roues. Toc-toc. Toc-toc. Un rayon glisse le long du rail en bois. Papa range une caisse près du canapé. Ça sent le bois et un peu la poussière. Tu as entendu le toc-toc, Raphaël ? Oui, papa. Les roues parlent. Elles parlent au parquet, oui. En ce moment, Raphaël pousse le train. Le wagon rouge suit la locomotive. Le rail est un peu lisse. Le train va sous la table. Doucement. La table a des pieds. Victorina s'assoit près du rail. Elle a un chausson qui glisse. Elle regarde le train. Je peux, Raphaël ? Raphaël tient le train un moment. Tu peux prêter, Raphaël. Prêter, c'est laisser Victorina pousser. Puis tu attends ton tour. Tu peux. C'est ton tour. Raphaël tend le train. Victorina pousse le wagon. Les roues tapent plus loin. Raphaël s'assoit près de papa. Il attend. Il compte les traverses du rail. Une. Deux. Trois. Tu attends ton tour. C'est du bon travail. Le rayon a bougé sur le rail. Victorina rend le train. C'est ton tour. Raphaël le fait rouler sous la table. Puis Victorina le voudrait encore. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Les cubes ? Oui. Les cubes font une gare. Raphaël prend des cubes. Victorina pose un cube jaune. Ils bâtissent une gare basse. Vous avez prêté. Chacun a eu son tour. Puis un autre jeu. Bravo, Raphaël. La gare est assez large ? Le train passe. C'est bien. Le parquet se tait un moment.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,20 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Thierry est dans le salon avec papa. Il fait rouler un train en bois. Les roues tapent le parquet. Clémentine arrive. Elle aimerait le train. Thierry peut prêter.
-narrateur|Tu peux. C'est ton tour. Il tend le train.
-narrateur|Clémentine pousse le wagon. Thierry attend son tour. Il s'assoit près de papa.
-papa|On peut prêter. On peut attendre son tour. On peut proposer un autre jeu.
-narrateur|Thierry prend des cubes.
-narrateur|Un autre jeu, les cubes.
-narrateur|Clémentine finit. Elle rend le train. Thierry le fait rouler. Parce qu'il a su prêter, le jeu continue. Papa tape dans ses mains.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>enfants_parc</t>
-        </is>
-      </c>
+          <t>narrateur|Le parquet chante sous les roues.
+narrateur|Toc-toc.
+narrateur|Toc-toc.
+narrateur|Un rayon glisse le long du rail en bois.
+narrateur|Papa range une caisse près du canapé.
+narrateur|Ça sent le bois et un peu la poussière.
+papa|Tu as entendu le toc-toc, Raphaël ?
+enfant-m|Oui, papa.
+enfant-m|Les roues parlent.
+papa|Elles parlent au parquet, oui.
+narrateur|En ce moment, Raphaël pousse le train.
+narrateur|Le wagon rouge suit la locomotive.
+narrateur|Le rail est un peu lisse.
+enfant-m|Le train va sous la table.
+papa|Doucement.
+papa|La table a des pieds.
+narrateur|Victorina s'assoit près du rail.
+narrateur|Elle a un chausson qui glisse.
+narrateur|Elle regarde le train.
+enfant-f|Je peux, Raphaël ?
+narrateur|Raphaël tient le train un moment.
+papa|Tu peux prêter, Raphaël.
+papa|Prêter, c'est laisser Victorina pousser.
+papa|Puis tu attends ton tour.
+enfant-m|Tu peux.
+enfant-m|C'est ton tour.
+narrateur|Raphaël tend le train.
+narrateur|Victorina pousse le wagon.
+narrateur|Les roues tapent plus loin.
+narrateur|Raphaël s'assoit près de papa.
+narrateur|Il attend.
+narrateur|Il compte les traverses du rail.
+enfant-m|Une.
+enfant-m|Deux.
+enfant-m|Trois.
+papa|Tu attends ton tour.
+papa|C'est du bon travail.
+narrateur|Le rayon a bougé sur le rail.
+narrateur|Victorina rend le train.
+enfant-f|C'est ton tour.
+narrateur|Raphaël le fait rouler sous la table.
+narrateur|Puis Victorina le voudrait encore.
+papa|Tu peux proposer un autre jeu.
+papa|Un autre jeu, c'est possible.
+enfant-m|Les cubes ?
+papa|Oui.
+papa|Les cubes font une gare.
+narrateur|Raphaël prend des cubes.
+narrateur|Victorina pose un cube jaune.
+narrateur|Ils bâtissent une gare basse.
+papa|Vous avez prêté.
+papa|Chacun a eu son tour.
+papa|Puis un autre jeu.
+papa|Bravo, Raphaël.
+papa|La gare est assez large ?
+enfant-m|Le train passe.
+papa|C'est bien.
+narrateur|Le parquet se tait un moment.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1350,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Clémentine veut le train. Que peut faire Thierry ?</t>
+          <t>Victorina veut le train. Que peut faire Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1565,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Clémentine veut le train. Que peut faire Thierry ?</t>
+          <t>narrateur|Victorina veut le train.
+narrateur|Que peut faire Raphaël ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Thierry a su prêter. Il a attendu son tour. Il a proposé un autre jeu.</t>
+          <t>Raphaël a su prêter. Il a attendu son tour. Il a proposé un autre jeu. Tu as prêté le train. Tu as attendu. Bravo, Raphaël. C'est du bon travail. Le cube jaune est en haut ? Non. Il est à côté. Un autre jeu, c'est bien aussi. Le rail reste au calme. Le rayon est plus court, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1738,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Thierry a su prêter. Il a attendu son tour. Il a proposé un autre jeu.</t>
+          <t>narrateur|Raphaël a su prêter.
+narrateur|Il a attendu son tour.
+narrateur|Il a proposé un autre jeu.
+papa|Tu as prêté le train.
+papa|Tu as attendu.
+papa|Bravo, Raphaël.
+papa|C'est du bon travail.
+papa|Le cube jaune est en haut ?
+enfant-m|Non.
+enfant-m|Il est à côté.
+papa|Un autre jeu, c'est bien aussi.
+narrateur|Le rail reste au calme.
+narrateur|Le rayon est plus court, maintenant.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Thierry et Clémentine rangent le train. Papa ferme la caisse.</t>
+          <t>Raphaël et Victorina rangent le train. Papa ferme la caisse. Les cubes aussi, dans la boîte ? Oui, papa. Les cubes tombent un à un. Tes genoux ont un peu de poussière. On les essuie ? Oui. Le canapé est doux sous la main. Merci d'avoir prêté. Merci d'avoir attendu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1914,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Thierry et Clémentine rangent le train. Papa ferme la caisse.</t>
+          <t>narrateur|Raphaël et Victorina rangent le train.
+narrateur|Papa ferme la caisse.
+papa|Les cubes aussi, dans la boîte ?
+enfant-m|Oui, papa.
+narrateur|Les cubes tombent un à un.
+papa|Tes genoux ont un peu de poussière.
+papa|On les essuie ?
+enfant-m|Oui.
+narrateur|Le canapé est doux sous la main.
+papa|Merci d'avoir prêté.
+papa|Merci d'avoir attendu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1952,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai prêté le train. Puis les cubes. Bravo. Tu as fait du bon travail. Le parquet ne chante plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2092,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai prêté le train.
+enfant-m|Puis les cubes.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le parquet ne chante plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2157,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.001-09.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-09.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le parquet chante sous les roues. Toc-toc. Toc-toc. Un rayon glisse le long du rail en bois. Papa range une caisse près du canapé. Ça sent le bois et un peu la poussière. Tu as entendu le toc-toc, Raphaël ? Oui, papa. Les roues parlent. Elles parlent au parquet, oui. En ce moment, Raphaël pousse le train. Le wagon rouge suit la locomotive. Le rail est un peu lisse. Le train va sous la table. Doucement. La table a des pieds. Victorina s'assoit près du rail. Elle a un chausson qui glisse. Elle regarde le train. Je peux, Raphaël ? Raphaël tient le train un moment. Tu peux prêter, Raphaël. Prêter, c'est laisser Victorina pousser. Puis tu attends ton tour. Tu peux. C'est ton tour. Raphaël tend le train. Victorina pousse le wagon. Les roues tapent plus loin. Raphaël s'assoit près de papa. Il attend. Il compte les traverses du rail. Une. Deux. Trois. Tu attends ton tour. C'est du bon travail. Le rayon a bougé sur le rail. Victorina rend le train. C'est ton tour. Raphaël le fait rouler sous la table. Puis Victorina le voudrait encore. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Les cubes ? Oui. Les cubes font une gare. Raphaël prend des cubes. Victorina pose un cube jaune. Ils bâtissent une gare basse. Vous avez prêté. Chacun a eu son tour. Puis un autre jeu. Bravo, Raphaël. La gare est assez large ? Le train passe. C'est bien. Le parquet se tait un moment.</t>
+          <t>Le parquet chante sous les roues. Toc-toc. Toc-toc. Un rayon glisse le long du rail en bois. Papa range une caisse près du canapé. Ça sent le bois et un peu la poussière. Tu as entendu le toc-toc, Raphaël ? Oui, papa. Les roues parlent. Elles parlent au parquet, oui. En ce moment, Raphaël pousse le train. Le wagon rouge suit la locomotive. Le rail est un peu lisse. Le train va sous la table. Doucement. La table a des pieds. Victorina s'assoit près du rail. Elle a un chausson qui glisse. Elle regarde le train. Je peux, Raphaël ? Raphaël tient le train un moment. Tu peux prêter, Raphaël. Prêter, c'est laisser Victorina pousser. Puis tu attends ton tour. Tu peux. C'est ton tour. Raphaël tend le train. Victorina pousse le wagon. Les roues tapent plus loin. Raphaël s'assoit près de papa. Il attend. Il compte les traverses du rail. Une. Deux. Trois. Tu attends ton tour. Le rayon a bougé sur le rail. Victorina rend le train. C'est ton tour. Raphaël le fait rouler sous la table. Puis Victorina le voudrait encore. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Les cubes ? Oui. Les cubes font une gare. Raphaël prend des cubes. Victorina pose un cube jaune. Ils bâtissent une gare basse. Vous avez prêté. Chacun a eu son tour. Puis un autre jeu. Bravo, Raphaël. La gare est assez large ? Le train passe. C'est bien. Le parquet se tait un moment.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Thierry est dans le salon avec papa. Il fait rouler un train en bois. Les roues tapent le parquet. Clémentine arrive. Elle aimerait le train. Thierry peut &lt;emphasis level="moderate"&gt;prêter&lt;/emphasis&gt;. Il dit : tu peux. C'est ton tour. Il tend le train. Clémentine pousse le wagon. Thierry attend son tour. Il s'assoit près de papa. Papa dit : on peut prêter. On peut attendre son tour. On peut proposer un autre jeu. Thierry prend des cubes. Il dit : un autre jeu, les cubes. Clémentine finit. Elle rend le train. Thierry le fait rouler. Parce qu'il a su prêter, le jeu continue. Papa tape dans ses mains.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le parquet chante sous les roues. Toc-toc. Toc-toc. Un rayon glisse le long du rail en bois. Papa range une caisse près du canapé. Ça sent le bois et un peu la poussière. Tu as entendu le toc-toc, Raphaël ? Oui, papa. Les roues parlent. Elles parlent au parquet, oui. En ce moment, Raphaël pousse le train. Le wagon rouge suit la locomotive. Le rail est un peu lisse. Le train va sous la table. Doucement. La table a des pieds. Victorina s'assoit près du rail. Elle a un chausson qui glisse. Elle regarde le train. Je peux, Raphaël ? Raphaël tient le train un moment. Tu peux prêter, Raphaël. Prêter, c'est laisser Victorina pousser. Puis tu attends ton tour. Tu peux. C'est ton tour. Raphaël tend le train. Victorina pousse le wagon. Les roues tapent plus loin. Raphaël s'assoit près de papa. Il attend. Il compte les traverses du rail. Une. Deux. Trois. Tu attends ton tour. Le rayon a bougé sur le rail. Victorina rend le train. C'est ton tour. Raphaël le fait rouler sous la table. Puis Victorina le voudrait encore. Tu peux proposer un autre jeu. Un autre jeu, c'est possible. Les cubes ? Oui. Les cubes font une gare. Raphaël prend des cubes. Victorina pose un cube jaune. Ils bâtissent une gare basse. Vous avez prêté. Chacun a eu son tour. Puis un autre jeu. Bravo, Raphaël. La gare est assez large ? Le train passe. C'est bien. Le parquet se tait un moment.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1360,7 +1360,6 @@
 enfant-m|Deux.
 enfant-m|Trois.
 papa|Tu attends ton tour.
-papa|C'est du bon travail.
 narrateur|Le rayon a bougé sur le rail.
 narrateur|Victorina rend le train.
 enfant-f|C'est ton tour.
@@ -1384,7 +1383,6 @@
 narrateur|Le parquet se tait un moment.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1414,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Clémentine veut le train. Que peut faire Thierry ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina veut le train. Que peut faire Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1569,7 +1567,6 @@
 narrateur|Que peut faire Raphaël ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a su prêter. Il a attendu son tour. Il a proposé un autre jeu. Tu as prêté le train. Tu as attendu. Bravo, Raphaël. C'est du bon travail. Le cube jaune est en haut ? Non. Il est à côté. Un autre jeu, c'est bien aussi. Le rail reste au calme. Le rayon est plus court, maintenant.</t>
+          <t>Raphaël a su prêter. Il a attendu son tour. Il a proposé un autre jeu. Tu as prêté le train. Tu as attendu. Bravo, Raphaël. Le cube jaune est en haut ? Non. Il est à côté. Un autre jeu, c'est bien aussi. Le rail reste au calme. Le rayon est plus court, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Thierry a su &lt;emphasis level="moderate"&gt;prêter&lt;/emphasis&gt;. Il a attendu son tour. Il a proposé un autre jeu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a su prêter. Il a attendu son tour. Il a proposé un autre jeu. Tu as prêté le train. Tu as attendu. Bravo, Raphaël. Le cube jaune est en haut ? Non. Il est à côté. Un autre jeu, c'est bien aussi. Le rail reste au calme. Le rayon est plus court, maintenant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1744,7 +1741,6 @@
 papa|Tu as prêté le train.
 papa|Tu as attendu.
 papa|Bravo, Raphaël.
-papa|C'est du bon travail.
 papa|Le cube jaune est en haut ?
 enfant-m|Non.
 enfant-m|Il est à côté.
@@ -1753,7 +1749,6 @@
 narrateur|Le rayon est plus court, maintenant.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,7 +1778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Thierry et Clémentine rangent le train. Papa ferme la caisse.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël et Victorina rangent le train. Papa ferme la caisse. Les cubes aussi, dans la boîte ? Oui, papa. Les cubes tombent un à un. Tes genoux ont un peu de poussière. On les essuie ? Oui. Le canapé est doux sous la main. Merci d'avoir prêté. Merci d'avoir attendu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1927,7 +1922,6 @@
 papa|Merci d'avoir attendu.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1952,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai prêté le train. Puis les cubes. Bravo. Tu as fait du bon travail. Le parquet ne chante plus. L'histoire est finie.</t>
+          <t>J'ai prêté le train. Puis les cubes. Bravo. Le parquet ne chante plus.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai prêté le train. Puis les cubes. Bravo. Le parquet ne chante plus.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2095,12 +2089,9 @@
           <t>enfant-m|J'ai prêté le train.
 enfant-m|Puis les cubes.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le parquet ne chante plus.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le parquet ne chante plus.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2119,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2164,6 +2155,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.001-09.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.001-09.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thierry, Clémentine, papa</t>
+          <t>Raphaël, Victorina, papa</t>
         </is>
       </c>
     </row>
